--- a/AAII_Financials/Quarterly/JPM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JPM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
   <si>
     <t>JPM</t>
   </si>
@@ -656,271 +656,277 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>54832000</v>
+      </c>
+      <c r="E8" s="3">
         <v>47329000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>41143000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>43024000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>42063000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>42005000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>40137000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>39543000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>47029000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>40066000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>35510000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>38390000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>35696000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>36074000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>33054000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>25611000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>18646000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>15496000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>15019000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>14480000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>14094000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>14271000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>14550000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>14700000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>16112000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>19161000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>19927000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>21121000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>21603000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>21389000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>19696000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>19840000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>18869000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>17695000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>16993000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>16687000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>30692000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>15042000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>14466000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>14070000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1041,53 +1047,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>54832000</v>
+      </c>
+      <c r="E10" s="3">
         <v>47329000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>41143000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>43024000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>42063000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>42005000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>40137000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>39543000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>47029000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>40066000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>35510000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>38390000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>35696000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>36074000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1163,8 +1172,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,53 +1467,56 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E14" s="3">
         <v>223000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-266000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>62000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>118000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-202000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>236000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>259000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>198000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>669000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3833000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>565000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-2292000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>176000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1573,91 +1592,94 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1619000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1603000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1600800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2269000</v>
       </c>
-      <c r="G15" s="3">
-        <v>2210000</v>
-      </c>
       <c r="H15" s="3">
+        <v>1627000</v>
+      </c>
+      <c r="I15" s="3">
         <v>1525000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>280000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1967000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2002000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2004000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1559000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2019000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>507000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1649000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-477000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-620000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-668000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-711000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>-785000</v>
       </c>
       <c r="V15" s="3">
         <v>-785000</v>
       </c>
       <c r="W15" s="3">
+        <v>-785000</v>
+      </c>
+      <c r="X15" s="3">
         <v>-876000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-934000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-996000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-1035000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-1084000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-1140000</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>0</v>
+      <c r="AD15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE15" s="3">
         <v>0</v>
@@ -1695,8 +1717,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>27200000</v>
+      </c>
+      <c r="E17" s="3">
         <v>26627000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24249000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>24219000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>23661000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>23799000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>22526000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>22306000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23396000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>22104000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20351000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>21092000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>20402000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>19931000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15150000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9630000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4619000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3087000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>130000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>-127000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>-932000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>-2774000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2303000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2598000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8332000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8607000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7188000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8407000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8354000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8431000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6890000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6880000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6594000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5548000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5274000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>5341000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>8950000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>4293000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3577000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3738000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>27632000</v>
+      </c>
+      <c r="E18" s="3">
         <v>20702000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>16894000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>18805000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>18402000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>18206000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>17611000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17237000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>23633000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>17962000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>15159000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>17298000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>15294000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>16143000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>17904000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>15981000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>14027000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>12409000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>14889000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>14607000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>15026000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>17045000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>12247000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>12102000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>7780000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>10554000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>12739000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>12714000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>13249000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>12958000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>12806000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>12960000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>12275000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>12147000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>11719000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>11346000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>21742000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>10749000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>10889000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>10332000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,8 +2056,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2068,208 +2101,214 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-4667000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3980000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3162000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2346000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2232000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-496000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>71000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>652000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2929000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-333000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2120000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-7344000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2174000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1309000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1907000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1725000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-3965000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2271000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1703000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1485000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-3465000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-1790000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-3652000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-2408000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-2210000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-1393000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>29251000</v>
+      </c>
+      <c r="E21" s="3">
         <v>22305000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>18494800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>21074000</v>
       </c>
-      <c r="G21" s="3">
-        <v>20612000</v>
-      </c>
       <c r="H21" s="3">
+        <v>20029000</v>
+      </c>
+      <c r="I21" s="3">
         <v>19731000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>17891000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>19204000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>25635000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>19966000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>16718000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>19317000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>15801000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>17792000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>14908000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>13772000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>12654000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>11883000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>14588000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>16039000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>17100000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>19767000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>17303000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>13910000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>7809000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>5407000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>12704000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>13550000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>13388000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>13271000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>10916000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>12681000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>12499000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>12459000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>9886000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>11135000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>21058000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>9805000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>10125000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>10346000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2312,8 +2351,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2390,252 +2429,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>27516000</v>
+      </c>
+      <c r="E23" s="3">
         <v>20479000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>17160000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>18743000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>18284000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>18408000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>17375000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>16978000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>23435000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>17293000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>11326000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>16733000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>17586000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>15967000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>13237000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>12001000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>10865000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>10063000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>12657000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>14111000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>15097000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>17697000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>15176000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>11769000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5660000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3210000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>10565000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>11405000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>11342000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>11233000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>8841000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>10689000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>10572000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>10662000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>8254000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>9556000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>18090000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>8341000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>8679000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>8939000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6361000</v>
+      </c>
+      <c r="E24" s="3">
         <v>3985000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4135000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4350000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3297000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3765000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3370000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4080000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5286000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3874000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2019000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3582000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3114000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3345000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2229000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2264000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2216000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1781000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2258000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2424000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3149000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3397000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3040000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2326000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>973000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>345000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2045000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2325000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1690000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2054000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2077000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2309000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>2256000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1950000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>2122000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>2824000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>4613000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1893000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>1952000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>2653000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>21155000</v>
+      </c>
+      <c r="E26" s="3">
         <v>16494000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>13025000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>14393000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14987000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>14643000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>14005000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>12898000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>18149000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>13419000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>9307000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>13151000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>14472000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>12622000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>11008000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>9737000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>8649000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>8282000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>10399000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>11687000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>11948000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>14300000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>12136000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>9443000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4687000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2865000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>8520000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>9080000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>9652000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>9179000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>6764000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>8380000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>8316000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>8712000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>6132000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>6732000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>13477000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>6448000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>6727000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>6286000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>20752000</v>
+      </c>
+      <c r="E27" s="3">
         <v>16148000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12690000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>14043000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14630000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>14317000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>13669000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>12537000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>17718000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>12942000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>8871000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>12685000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>14011000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>12193000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>10597000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>9255000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>8195000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>7845000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>9927000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>11229000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>11496000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>13851000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>11698000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>9015000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4265000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2431000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>8091000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>8606000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>9192000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>8753000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>6340000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>7948000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>7880000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>8238000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>5681000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>6262000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>12524000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>5975000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>6250000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>5812000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3196,8 +3256,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
@@ -3214,24 +3274,24 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>302000</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-1900000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,8 +3554,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3532,208 +3601,214 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>4667000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3980000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3162000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2346000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2232000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>496000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-71000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-652000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2929000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>333000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2120000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>7344000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2174000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1309000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1907000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1725000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>3965000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2271000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1703000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1485000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>3465000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>1790000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>3652000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>2408000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>2210000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>1393000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>21155000</v>
+      </c>
+      <c r="E33" s="3">
         <v>16494000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>13025000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>14393000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14987000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>14643000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>14005000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>12898000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>18149000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>13419000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>9307000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>13151000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>14472000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>12622000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>10597000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>9255000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>8195000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>7845000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>9927000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>11229000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>11496000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>13851000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>11698000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>9015000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4265000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2431000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>8091000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>8606000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>9192000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>8753000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>6642000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>7948000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>7880000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>8238000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>3781000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>6262000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>12524000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>5975000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>6250000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>5812000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>21155000</v>
+      </c>
+      <c r="E35" s="3">
         <v>16494000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>13025000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>14393000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14987000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>14643000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>14005000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>12898000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>18149000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>13419000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>9307000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>13151000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>14472000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>12622000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>10597000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>9255000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>8195000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>7845000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>9927000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>11229000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>11496000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>13851000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>11698000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>9015000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4265000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2431000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>8091000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>8606000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>9192000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>8753000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>6642000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>7948000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>7880000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>8238000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>3781000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>6262000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>12524000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>5975000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>6250000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>5812000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,252 +4276,259 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>286120000</v>
+      </c>
+      <c r="E41" s="3">
         <v>285242000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>314338000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>274685000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>393734000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>397003000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>441847000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>409160000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>507909000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>541716000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>604576000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>488231000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>469592000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>524464000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>540434000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>617087000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>638360000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>723732000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>721134000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>738569000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>686421000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>689972000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>527609000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>487522000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>493729000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>367534000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>263631000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>256597000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>268038000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>21946000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>22324000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>23225000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>23680000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>24834000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>25827000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>21994000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>21781000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>20484000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>23873000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>21390000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1240299000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1297004000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>973372000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1136342000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1143858000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1081702000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>796685000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1014883000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>949619000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1084968000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>687740000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>819240000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>962555000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>895939000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>883880000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>909047000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>908809000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>964619000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>844263000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>933141000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>897240000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>922930000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>880415000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>891486000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>850880000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>855351000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>750252000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>836025000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>869020000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1186053000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1049553000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1095703000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1076540000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1109086000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1033149000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1085102000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1087162000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>1069236000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>1000190000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>1047292000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4479,8 +4571,8 @@
       <c r="P43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -4557,53 +4649,56 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>314000</v>
+      </c>
+      <c r="E44" s="3">
         <v>141000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>134000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>122000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>111000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>116000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>112000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>343000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>128000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>146000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>162000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>158000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>162000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>160000</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
@@ -4679,53 +4774,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>810333000</v>
+      </c>
+      <c r="E45" s="3">
         <v>617041000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>516372000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>563943000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>511911000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>530142000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>404900000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>485149000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>455261000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>276108000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>389146000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>405381000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>232360000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>267267000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2376531000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2242357000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1847056000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2014667000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2089433000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2048035000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1678092000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1947139000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1945720000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1929815000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1705209000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1741520000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1695861000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1714930000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,53 +5024,56 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>822944000</v>
+        <v>807018000</v>
       </c>
       <c r="E47" s="3">
+        <v>828741000</v>
+      </c>
+      <c r="F47" s="3">
         <v>782205000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>785591000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>747803000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>666178000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>685057000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>635940000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>590962000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>606547000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>576009000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>587057000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>613332000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>611807000</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -5045,252 +5149,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>59201000</v>
+      </c>
+      <c r="E48" s="3">
         <v>57671000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>56851000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>53563000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>49662000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>47411000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>45775000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>43025000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>41582000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>40779000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>41334000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>40277000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>40393000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>39566000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>27734000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>27199000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>26770000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>26916000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>27070000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>26996000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>26631000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>26926000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>27109000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>26672000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>26301000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>25882000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>25813000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>25117000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>24665000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>24160000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>14934000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>14180000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>14132000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>14382000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>14159000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>14218000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>14206000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>14227000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>14131000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>14208000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>64304000</v>
+      </c>
+      <c r="E49" s="3">
         <v>64289000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>64458000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>64442000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>64465000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>64525000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>64560000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>64455000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>64525000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>64374000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>64381000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>64910000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>64238000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>62090000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>60859000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>60806000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>59360000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>58485000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>56691000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>56566000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>54655000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>54588000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>53428000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>51594000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>51669000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>51867000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>53341000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>53078000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>53302000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>54168000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>54349000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>54697000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>54535000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>54533000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>54392000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>53855000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>53880000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>54218000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>54246000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>53126000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,53 +5649,56 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>186799000</v>
+        <v>207470000</v>
       </c>
       <c r="E52" s="3">
+        <v>181002000</v>
+      </c>
+      <c r="F52" s="3">
         <v>166213000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>174704000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>174191000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>161980000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>148621000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>162654000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>155879000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>116373000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>133364000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>138366000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>139155000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>168603000</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -5655,8 +5774,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5015069000</v>
+      </c>
+      <c r="E54" s="3">
         <v>4900475000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4424900000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4560205000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4552482000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4357856000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4002814000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4210048000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4143003000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4090727000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3875393000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3898333000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3868240000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3744305000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3665743000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3773884000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3841314000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3954687000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3743567000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3757576000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3684256000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3689336000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3384757000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3246076000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3213115000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3139431000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2687379000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2764661000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2727379000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2737188000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2622532000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2615183000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2590050000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>2609785000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>2533600000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>2563074000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>2563174000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>2546290000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>2490972000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>2521029000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,178 +6116,182 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3048382000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2987057000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2652448000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2829037000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2829390000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2755556000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2502250000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2713211000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2660957000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2697082000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2498328000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2647924000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2662754000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2630347000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>291958000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>291782000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>305000000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>312322000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>254427000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>260342000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>288796000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>276645000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>222777000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>225921000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>222490000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>245358000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>201902000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>216638000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>207733000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>207611000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>196710000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>209707000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>196984000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>192295000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>189383000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>196764000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>189160000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>183200000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>190543000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>190412000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>861699000</v>
+      </c>
+      <c r="E58" s="3">
         <v>835961000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>570802000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>683332000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>708743000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>635258000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>389389000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>484505000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>488883000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>416858000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>302094000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>401466000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>395784000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>333348000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>271799000</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
       <c r="S58" s="3">
         <v>0</v>
       </c>
@@ -6231,101 +6364,104 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>227031000</v>
+      </c>
+      <c r="E59" s="3">
         <v>207284000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>176290000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>204016000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>182192000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>157771000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>159122000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>204593000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>206018000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>192324000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>145181000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>165494000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>132264000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>145153000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8183000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8234000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>8326000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>8349000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>8328000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>8262000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>8286000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8421000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8508000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8335000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8426000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8516000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8505000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8425000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>8404000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8562000</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>5</v>
       </c>
@@ -6335,8 +6471,8 @@
       <c r="AJ59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK59" s="3">
-        <v>0</v>
+      <c r="AK59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AL59" s="3">
         <v>0</v>
@@ -6353,53 +6489,56 @@
       <c r="AP59" s="3">
         <v>0</v>
       </c>
+      <c r="AQ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4153712000</v>
+      </c>
+      <c r="E60" s="3">
         <v>4046202000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3602198000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3732285000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3735825000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3563185000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3218314000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3416609000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3369658000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3319464000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3120763000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3227784000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3203002000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3120348000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,175 +6614,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>481608000</v>
+      </c>
+      <c r="E61" s="3">
         <v>485144000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>455193000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>464744000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>456801000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>441025000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>437641000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>444692000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>429871000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>432710000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>423678000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>351103000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>350536000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>318505000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>259613000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>276375000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>277109000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>282131000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>301005000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>298465000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>299926000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>279427000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>281685000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>279175000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>317003000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>299344000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>291498000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>296472000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>288869000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>290893000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>282031000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>270124000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>273114000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>274449000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>284080000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>288582000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>292973000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>289492000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>295245000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>309418000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5151000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5091000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5071000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2964000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2932000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2226000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2101000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2911000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2922000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1916000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3074000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2075000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2186000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2370000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6719,8 +6864,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4640471000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4536437000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4062462000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4199993000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4195558000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4006436000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3658056000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3864212000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3802451000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3754090000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3547515000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3580962000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3555724000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3441223000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3373411000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3485866000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3555171000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3668788000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3449440000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3467535000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3397870000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3408622000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3105403000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2974963000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2948649000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2878169000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2426049000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2500313000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2464164000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2477351000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2366017000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2356227000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2332592000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2353584000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2277907000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2304692000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>2304691000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>2290427000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>2236782000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>2266698000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,13 +7659,16 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>20045000</v>
+        <v>21040000</v>
       </c>
       <c r="E70" s="3">
         <v>20045000</v>
@@ -7516,19 +7683,19 @@
         <v>20045000</v>
       </c>
       <c r="I70" s="3">
+        <v>20045000</v>
+      </c>
+      <c r="J70" s="3">
         <v>20050000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>21650000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>23900000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>29900000</v>
-      </c>
-      <c r="M70" s="3">
-        <v>27404000</v>
       </c>
       <c r="N70" s="3">
         <v>27404000</v>
@@ -7543,7 +7710,7 @@
         <v>27404000</v>
       </c>
       <c r="R70" s="3">
-        <v>32838000</v>
+        <v>27404000</v>
       </c>
       <c r="S70" s="3">
         <v>32838000</v>
@@ -7552,19 +7719,19 @@
         <v>32838000</v>
       </c>
       <c r="U70" s="3">
-        <v>34838000</v>
+        <v>32838000</v>
       </c>
       <c r="V70" s="3">
         <v>34838000</v>
       </c>
       <c r="W70" s="3">
+        <v>34838000</v>
+      </c>
+      <c r="X70" s="3">
         <v>32838000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>31563000</v>
-      </c>
-      <c r="Y70" s="3">
-        <v>30063000</v>
       </c>
       <c r="Z70" s="3">
         <v>30063000</v>
@@ -7576,25 +7743,25 @@
         <v>30063000</v>
       </c>
       <c r="AC70" s="3">
+        <v>30063000</v>
+      </c>
+      <c r="AD70" s="3">
         <v>26993000</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>28363000</v>
-      </c>
-      <c r="AE70" s="3">
-        <v>26993000</v>
       </c>
       <c r="AF70" s="3">
         <v>26993000</v>
       </c>
       <c r="AG70" s="3">
+        <v>26993000</v>
+      </c>
+      <c r="AH70" s="3">
         <v>26068000</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>27764000</v>
-      </c>
-      <c r="AI70" s="3">
-        <v>26068000</v>
       </c>
       <c r="AJ70" s="3">
         <v>26068000</v>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>26068000</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>26068000</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>445020000</v>
+      </c>
+      <c r="E72" s="3">
         <v>428206000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>416055000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>407401000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>397424000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>386616000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>376166000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>365966000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>356924000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>342414000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>332901000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>327044000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>317359000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>306208000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>296456000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>288776000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>282445000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>277177000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>272268000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>265276000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>256983000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>248151000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>236990000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>228014000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>221732000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>220226000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>223211000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>217888000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>212093000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>205437000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>199202000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>195180000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>189881000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>183855000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>177676000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>175827000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>171488000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>166663000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>162440000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>157870000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>353558000</v>
+      </c>
+      <c r="E76" s="3">
         <v>343993000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>342393000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>340167000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>336879000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>331375000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>324708000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>324186000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>316652000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>306737000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>300474000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>289967000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>285112000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>275678000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>264928000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>255180000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>253305000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>253061000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>259289000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>255203000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>253548000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>249151000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>249291000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>241050000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>234403000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>231199000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>234337000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>235985000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>236222000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>232844000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>230447000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>231192000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>231390000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>230133000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>229625000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>232314000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>232415000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>229795000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>228122000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>228263000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>21155000</v>
+      </c>
+      <c r="E81" s="3">
         <v>16494000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>13025000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>14393000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14987000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>14643000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>14005000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>12898000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>18149000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>13419000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>9307000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>13151000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>14472000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>12622000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>10597000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>9255000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>8195000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>7845000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>9927000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>11229000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>11496000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>13851000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>11698000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>9015000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4265000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2431000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>8091000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>8606000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>9192000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>8753000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>6642000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>7948000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>7880000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>8238000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>3781000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>6262000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>12524000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>5975000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>6250000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>5812000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2210000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2030000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1626000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1967000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2002000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2004000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3022000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2019000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>507000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1649000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1671000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1771000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1789000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1820000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1671000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1771000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1789000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1820000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1931000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1928000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2003000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2070000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2127000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2141000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2149000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2197000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2139000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>2145000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>2046000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>2038000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>2075000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1992000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1927000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1797000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1632000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1579000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>2968000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>1464000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>1446000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>1407000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-25283000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-211761000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>119724000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-45214000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>29547000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-251839000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>147758000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-74081000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>38469000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-154158000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>60231000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>45119000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>18865000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-111241000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>101222000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-18204000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>66018000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-41917000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>85095000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>23331000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>13530000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-43872000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-28051000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-14827000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>83057000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-120089000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>83085000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>17695000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-13854000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-80880000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>422000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>13189000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>35685000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-35109000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>13537000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-3014000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-13024000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-20036000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>38911000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>4192000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,8 +9881,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9706,8 +9926,8 @@
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9748,8 +9968,8 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>5</v>
+      <c r="AE91" s="3">
+        <v>0</v>
       </c>
       <c r="AF91" s="3" t="s">
         <v>5</v>
@@ -9760,8 +9980,8 @@
       <c r="AH91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI91" s="3">
-        <v>0</v>
+      <c r="AI91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AJ91" s="3">
         <v>0</v>
@@ -9784,8 +10004,11 @@
       <c r="AP91" s="3">
         <v>0</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>6393000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-217769000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>46882000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-21311000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-173060000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-118076000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>17620000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-43405000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-94239000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-43379000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>79882000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-17790000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-18243000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>23794000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-51530000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>39522000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-53203000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-72608000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-100158000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-62275000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>17698000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>15391000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-63706000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-14727000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-48329000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-135150000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-13878000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-65605000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-8877000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>36301000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-158211000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-808000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>6047000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-45021000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-19457000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>23167000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>24539000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>47112000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-2847000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-60038000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,8 +10426,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10238,86 +10471,89 @@
       <c r="P96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R96" s="3">
         <v>-3020000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2980000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2934000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-3033000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2960000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2756000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-2728000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-2814000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-2759000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-2828000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-2753000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-2767000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-3287000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-2975000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-3048000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-3033000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-3120000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-2273000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-2480000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-2236000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-2515000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-2092000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-4386000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-2045000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-2287000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-2069000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,370 +10924,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>18802000</v>
+      </c>
+      <c r="E100" s="3">
         <v>400677000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-123557000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-47773000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>122804000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>318059000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-115705000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>10746000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>27238000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>141168000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-35897000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4316000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-49915000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>64557000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-142344000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-32883000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-83802000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>132772000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2022000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>97047000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-37943000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>218911000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>125958000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>19251000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>89131000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>362305000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-63019000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>39537000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-12966000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>69435000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>17839000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>2553000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-46823000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>60589000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-21763000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-11506000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>47911000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>43605000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-33428000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>57540000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>15133000</v>
+      </c>
+      <c r="E101" s="3">
         <v>8442000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-14616000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>10181000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2765000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5666000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>8566000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-6767000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1584000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1656000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>15699000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-13508000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-14285000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4549000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>15699000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-13508000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-14285000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4549000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1950000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3655000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1064000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-6967000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>5887000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>3957000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1791000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2480000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>2800000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-3068000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1131000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1045000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-354000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1017000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-4541000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>3049000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>814000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>1864000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>5408000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>2574000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-153000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-14000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2331000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-31196000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>39902000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-116891000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5576000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-43414000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>35057000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-96559000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-31297000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-62035000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>112782000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>16246000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-50877000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-21234000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-76953000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-25073000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-85272000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>13698000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-19035000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>54448000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-5651000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>183463000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>40087000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6207000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>126195000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>103903000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>7034000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-11441000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-34566000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>23811000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-140304000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>13917000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-9632000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-16492000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-27852000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>8630000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>59372000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>70732000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>2483000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>1680000</v>
       </c>
     </row>
